--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/10_ai_automation_use_cases.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/10_ai_automation_use_cases.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8172249029ac4617"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R862f0bfb3e7640f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Re3cfc5c992224479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R349c4bb2d1d2411f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Re5e8606cd605429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rcb5d593ef6c94385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rfb8cbb04c80f4b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R79a3680a10ef4873"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rd0a99d7cc4e34c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rec6d82510dc145de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R6b8d34c7552b49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rc3df54de756e4852"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -626,7 +626,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5a41fb5fe54c39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd796b83fea2b4b34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -797,7 +797,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="N6" s="78" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Executive Office context and decision assistant (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -844,7 +844,7 @@
         <x:v>Retail Banking COO</x:v>
       </x:c>
       <x:c r="N7" s="79" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Retail Deposits and Branch Operations context and decision assistant (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -891,7 +891,7 @@
         <x:v>Commercial Banking COO</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury context and decision assistant (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O8" t="str">
         <x:v>Medium</x:v>
@@ -938,7 +938,7 @@
         <x:v>Head of Cards</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Cards Operations context and decision assistant (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O9" t="str">
         <x:v>Medium</x:v>
@@ -985,7 +985,7 @@
         <x:v>Payments Leader</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations context and decision assistant (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O10" t="str">
         <x:v>Medium</x:v>
@@ -1032,7 +1032,7 @@
         <x:v>Head of Consumer Lending</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Consumer Lending Operations context and decision assistant (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O11" t="str">
         <x:v>Medium</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>Head of Wealth</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage context and decision assistant (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O12" t="str">
         <x:v>Medium</x:v>
@@ -1126,7 +1126,7 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Fraud / risk AI-enabled workflow (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O13" t="str">
         <x:v>Medium</x:v>
@@ -1173,7 +1173,7 @@
         <x:v>Chief Compliance Officer</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Compliance and Model Risk Management context and decision assistant (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O14" t="str">
         <x:v>Medium</x:v>
@@ -1220,7 +1220,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing context and decision assistant (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O15" t="str">
         <x:v>Medium</x:v>
@@ -1267,7 +1267,7 @@
         <x:v>Digital Banking Product Owner</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Digital onboarding AI-enabled workflow (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O16" t="str">
         <x:v>Medium</x:v>
@@ -1314,7 +1314,7 @@
         <x:v>CIO</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Core Banking Modernization context and decision assistant (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O17" t="str">
         <x:v>Medium</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Customer 360 AI-enabled workflow (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O18" t="str">
         <x:v>Medium</x:v>
@@ -1408,7 +1408,7 @@
         <x:v>Retail Analytics Lead</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile Retail Banking Analytics context and decision assistant (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O19" t="str">
         <x:v>Medium</x:v>
@@ -1455,7 +1455,7 @@
         <x:v>Cards Analytics Lead</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics context and decision assistant (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O20" t="str">
         <x:v>Medium</x:v>
@@ -1502,7 +1502,7 @@
         <x:v>Payments Analytics Lead</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Payments and Settlement Analytics context and decision assistant (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O21" t="str">
         <x:v>Medium</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Fraud/risk analytics AI-enabled workflow (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="O22" t="str">
         <x:v>Medium</x:v>
@@ -1596,7 +1596,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform context and decision assistant (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="O23" t="str">
         <x:v>Medium</x:v>
@@ -1643,7 +1643,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline context and decision assistant (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="O24" t="str">
         <x:v>Medium</x:v>
@@ -1690,7 +1690,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization context and decision assistant (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="O25" t="str">
         <x:v>Medium</x:v>
@@ -1737,7 +1737,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Validate Infrastructure and CMDB context and decision assistant (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for ai automation use cases.</x:v>
       </x:c>
       <x:c r="O26" t="str">
         <x:v>Medium</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>Need production data access, model risk/privacy approval, evaluation set, and adoption baseline.</x:v>
+        <x:v>Confirm Incident Problem Change Operations context and decision assistant (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this ai automation use cases record is used downstream.</x:v>
       </x:c>
       <x:c r="O27" t="str">
         <x:v>Medium</x:v>
@@ -1808,7 +1808,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabc0a162f5a4fea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18e8beebae4e4f50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1883,7 +1883,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08e383e783b8449e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8da1ed3f3d47f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2067,7 +2067,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R093647bf161641c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd84ce37b1ba643eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2137,7 +2137,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R498d7c53fe054a83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22597b967ac6408c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2247,7 +2247,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0633b9f0284704"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5ccfcc530b47a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>